--- a/artfynd/A 22776-2026 artfynd.xlsx
+++ b/artfynd/A 22776-2026 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>134216897</v>
       </c>
       <c r="B5" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134216915</v>
       </c>
       <c r="B7" t="n">
-        <v>96396</v>
+        <v>96398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>134216913</v>
       </c>
       <c r="B8" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>134216916</v>
       </c>
       <c r="B9" t="n">
-        <v>91977</v>
+        <v>91979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22776-2026 artfynd.xlsx
+++ b/artfynd/A 22776-2026 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>134216897</v>
       </c>
       <c r="B5" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>134216915</v>
       </c>
       <c r="B7" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>134216913</v>
       </c>
       <c r="B8" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>134216916</v>
       </c>
       <c r="B9" t="n">
-        <v>91980</v>
+        <v>91987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22776-2026 artfynd.xlsx
+++ b/artfynd/A 22776-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134216921</v>
+        <v>134216897</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753080</v>
+        <v>753072</v>
       </c>
       <c r="R2" t="n">
-        <v>7107652</v>
+        <v>7107720</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134216914</v>
+        <v>134216915</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>96413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -902,53 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134216898</v>
+        <v>134216899</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752996</v>
+        <v>752941</v>
       </c>
       <c r="R4" t="n">
-        <v>7107758</v>
+        <v>7107754</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134216897</v>
+        <v>134216914</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753072</v>
+        <v>753070</v>
       </c>
       <c r="R5" t="n">
-        <v>7107720</v>
+        <v>7107739</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1110,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1233,48 +1210,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134216915</v>
+        <v>134216898</v>
       </c>
       <c r="B7" t="n">
-        <v>96406</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brattfäbodberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753070</v>
+        <v>752996</v>
       </c>
       <c r="R7" t="n">
-        <v>7107739</v>
+        <v>7107758</v>
       </c>
       <c r="S7" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,42 +1327,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134216913</v>
+        <v>134216921</v>
       </c>
       <c r="B8" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1383,13 +1370,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753121</v>
+        <v>753080</v>
       </c>
       <c r="R8" t="n">
-        <v>7107841</v>
+        <v>7107652</v>
       </c>
       <c r="S8" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,12 +1415,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På två ställen, täcker ett ca 30 x 30 cm stort område respektive</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,7 +1429,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1461,30 +1447,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134216916</v>
+        <v>134216918</v>
       </c>
       <c r="B9" t="n">
-        <v>91987</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1492,13 +1482,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753133</v>
+        <v>753205</v>
       </c>
       <c r="R9" t="n">
-        <v>7107750</v>
+        <v>7107739</v>
       </c>
       <c r="S9" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1537,7 +1527,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 22776-2026 artfynd.xlsx
+++ b/artfynd/A 22776-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216897</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216915</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216899</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216914</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216898</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216921</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,8 +1591,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134216918</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>